--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3316,7 +3316,7 @@
         <v>121326284</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3436,6 +3436,130 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129479846</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98712</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sandemars naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>693593</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6560528</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca 5 m till hyggeskanten</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 13137-2022 artfynd.xlsx
+++ b/artfynd/A 13137-2022 artfynd.xlsx
@@ -3441,7 +3441,7 @@
         <v>129479846</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
